--- a/experiments/rq1-3-4-5/summary/visidroid_no_vision_evals.xlsx
+++ b/experiments/rq1-3-4-5/summary/visidroid_no_vision_evals.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="645">
   <si>
     <t>app_name</t>
   </si>
@@ -1011,11 +1011,16 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "add holidays"
-- action 3: touched on a button that has text "south africa"
-- action 4: touched on a button that has text "ok"
-- action 5: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "add holidays"
+- action 5: jade green touched on a button that has text "south africa"
+- action 6: jade green touched on a button that has text "ok"
+- action 7: jade green touched on a button that has content_desc "filter events by type"
+- action 8: jade green touched on a button that has text "ok"
+- action 9: jade green touched on a button that has content_desc "search"
+- action 10: jade green filled a focused textfield that has text "search" with the text "2023"
+- action 11: jade green touched on a button that has content_desc "change view"
+- action 12: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "more options"
@@ -1038,34 +1043,38 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "new event"
-- action 2: touched on a button that has content-desc "new event"
-- action 3: filled a focused textfield that has text "title" with the text "john doe's anniversary"
-- action 4: touched on a button that has text "october 25 (fri)"
-- action 5: touched on a button that has text "ok"
-- action 6: touched on a button that has text "no repetition"
-- action 7: touched on a button that has text "yearly"
-- action 8: touched on a button that has content-desc "save"
+    <t>- action 1: jade green touched on a button that has content_desc "new event"
+- action 2: jade green touched on a button that has text "event"
+- action 3: jade green filled a focused textfield that has text "title" with the text "[contact's name] anniversary"
+- action 4: jade green touched on a button that has text "february 24 (mon)"
+- action 5: jade green touched on a button that has text "ok"
+- action 6: jade green touched on a button that has text "no repetition"
+- action 7: jade green touched on a button that has text "yearly"
+- action 8: jade green touched on a button that has content_desc "save"
 - action 9: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "new event"
-- action 2: touched on a button that has content-desc "new event"
-- action 3: filled a focused textfield that has text "title" with the text "visitparents"
-- action 4: touched on a button that has text "october 25 (fri)"
-- action 6: touched on a button that has content-desc "next month"
-- action 7: touched on a button that has text "30"
-- action 8: touched on a button that has text "ok"
-- action 9: touched on a button that has text "1 hour before"
-- action 10: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a button that has text "customize notifications"
-- action 4: touched on a button that has text "deadlines, ~2 notifications per week"
-- action 5: touched on a button that has text "advanced, sound, vibration, override do not disturb"
-- action 6: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "new event"
+- action 2: jade green filled a focused textfield that has text "title" with the text "visitparents"
+- action 3: jade green touched on a button that has text "february 24 (mon)"
+- action 5: jade green touched on a button that has text "30"
+- action 6: jade green touched on a button that has content_desc "previous month"
+- action 7: jade green touched on a button that has text "30"
+- action 8: jade green touched on a button that has content_desc "next month"
+- action 9: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: jade green touched on a button that has text "customize notifications"
+- action 4: jade green touched on a button that has text "advanced, allow notification dot"
+- action 5: jade green touched on a button that has text "calendar"
+- action 6: jade green touched on a button that has content_desc "back"
+- action 7: jade green touched on a button that has text "customize notifications"
+- action 8: jade green touched on a button that has text "advanced, allow notification dot"
+- action 9: jade green touched on a button that has content_desc "back"
+- action 10: jade green touched on a button that has text "customize notifications"
+- action 11: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "more options"
@@ -1077,15 +1086,11 @@
 - action 7: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "search"
-- action 2: filled a focused textfield that has text "search" with the text "snooze time"
-- action 3: touched on a button that has content-desc "more options"
-- action 4: touched on a button that has text "settings"
-- action 5: touched on a button that has text "customize notifications"
-- action 6: touched on a button that has content-desc "search settings"
-- action 7: touched on a button that has content-desc "navigate up"
-- action 8: touched on a button that has content-desc "back"
-- action 9: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 4: jade green touched on a button that has text "snooze time, 10 minutes"
+- action 5: jade green touched on a button that has text "30 minutes"
+- action 6: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "change view"
@@ -1093,36 +1098,30 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "new event"
-- action 2: touched on a button that has content-desc "new event"
-- action 3: filled a focused textfield that has text "title" with the text "laundry"
-- action 4: touched on a button that has content-desc "save"
-- action 5: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/small_month_view"
-- action 2: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- action 3: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has content-desc "more options"
-- action 6: touched on a button that has content-desc "change view"
-- action 7: touched on a button that has text "monthly view"
-- action 8: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- action 9: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- action 10: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a button that has text "manage event types"
-- action 4: touched on a button that has content-desc "back"
-- action 5: touched on a button that has content-desc "back"
-- action 6: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "filter events by type"
-- action 8: touched on a button that has text "cancel"
-- action 9: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/small_month_view"
-- action 10: touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
-- action 11: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "new event"
+- action 2: jade green filled a focused textfield that has text "title" with the text "laundry"
+- action 3: jade green touched on a button that has content_desc "save"
+- action 4: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "new event"
+- action 2: jade green filled a focused textfield that has text "title" with the text "homework"
+- action 3: jade green touched on a button that has text "no repetition"
+- action 4: jade green touched on a button that has text "daily"
+- action 5: jade green touched on a button that has content_desc "save"
+- action 6: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: jade green touched on a button that has text "manage event types"
+- action 4: jade green touched on a button that has content_desc "back"
+- action 6: jade green touched on a button that has content_desc "more options"
+- action 8: jade green touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
+- action 9: jade green touched on a button that has content_desc "go to today"
+- action 10: jade green touched on a button that has resource_id "com.simplemobiletools.calendar.pro:id/month_view_background"
+- action 11: jade green touched on a button that has content_desc "delete"
+- action 12: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "more options"
@@ -1131,16 +1130,15 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a button that has content-desc "back"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has text "print"
-- action 6: touched on a button that has content-desc "save to pdf"
-- action 7: touched on a button that has content-desc "more options"
-- action 8: touched on a button that has text "settings"
-- action 9: touched on a button that has content-desc "back"
-- action 10: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "print"
+- action 4: jade green touched on a button that has content_desc "more options"
+- action 5: jade green touched on a button that has text "go to date"
+- action 6: jade green touched on a button that has text "cancel"
+- action 7: jade green touched on a button that has content_desc "more options"
+- action 9: jade green touched on a button that has content_desc "more options"
+- action 10: jade green touched on a button that has text "settings"
+- action 12: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "search"
@@ -1148,20 +1146,15 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "view last captured media"
-- action 2: touched on a button that has content-desc "view last captured media"
-- action 3: waited for a loading state to finish
-- action 4: touched on a button that has content-desc "view last captured media"
-- action 5: waited for a loading state to finish
-- action 6: touched on a button that has content-desc "view last captured media"
-- action 7: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: waited for a loading state to finish
-- action 2: touched on a button that has content-desc "view last captured media"
-- action 3: touched on a button that has content-desc "more options"
-- action 4: touched on a button that has text "details"
-- action 5: task completed?</t>
+    <t>- action 1: jade green waited for a loading state to finish
+- action 2: jade green touched on a button that has content_desc "view last captured media"
+- action 3: jade green touched on a button that has content_desc "more options"
+- action 4: task completed?</t>
+  </si>
+  <si>
+    <t>- action 2: jade green touched on a button that has content_desc "view last captured media"
+- action 3: jade green touched on a button that has content_desc "more options"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -1170,21 +1163,25 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "view last captured media"
-- action 2: touched on a button that has content-desc "view last captured media"
-- action 3: touched on a button that has content-desc "view last captured media"
-- action 4: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "view last captured media"
-- action 2: touched on a button that has content-desc "more options"
-- action 3: touched on a button that has text "details"
-- action 4: touched on a button that has text "close"
-- action 5: touched on a button that has content-desc "view last captured media"
-- action 6: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "more options"
-- action 8: touched on a button that has content-desc "dcim, navigate up"
-- action 9: touched on a button that has content-desc "dcim, navigate up"
+    <t>- action 1: jade green waited for a loading state to finish
+- action 2: jade green touched on a button that has text "gallery"
+- action 3: jade green touched on a button that has content_desc "view last captured media"
+- action 4: jade green touched on a button that has content_desc "more options"
+- action 5: jade green touched on a button that has content_desc "dcim, navigate up"
+- action 6: jade green touched on a button that has content_desc "share with print"
+- action 7: jade green long touched on a button that has content_desc "more options"
+- action 9: jade green touched on a button that has content_desc "view last captured media"
+- action 10: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green waited for a loading state to finish
+- action 2: jade green touched on a button that has content_desc "view last captured media"
+- action 3: jade green touched on a button that has resource_id "android:id/expand_activities_button"
+- action 4: jade green touched on a button that has content_desc "more options"
+- action 5: jade green long touched on a button that has content_desc "more options"
+- action 7: jade green touched on a button that has content_desc "view last captured media"
+- action 8: jade green touched on a button that has content_desc "more options"
+- action 9: jade green long touched on a button that has content_desc "more options"
 - action 10: task completed?</t>
   </si>
   <si>
@@ -1192,73 +1189,58 @@
 - action 2: task completed?</t>
   </si>
   <si>
-    <t>- action 1: waited for a loading state to finish
-- action 2: touched on a button that has content-desc "view last captured media"
-- action 3: touched on a button that has resource_id "android:id/expand_activities_button"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has resource_id "android:id/expand_activities_button"
-- action 6: touched on a button that has text "print"
-- action 7: touched on a button that has content-desc "view last captured media"
-- action 8: touched on a button that has content-desc "share with print"
-- action 9: touched on a button that has content-desc "share with print"
-- action 10: touched on a button that has content-desc "share with print"
-- action 11: touched on a button that has content-desc "share with print"
+    <t>- action 1: jade green touched on a button that has content_desc "view last captured media"
+- action 2: jade green touched on a button that has content_desc "share with print"
+- action 3: task completed?</t>
+  </si>
+  <si>
+    <t>- action 2: jade green touched on a button that has text "video"
+- action 3: jade green touched on a button that has content_desc "shutter"
+- action 4: jade green touched on a selected button that has content_desc "shutter"
+- action 5: jade green touched on a button that has content_desc "shutter"
+- action 6: jade green touched on a selected button that has content_desc "shutter"
+- action 7: jade green touched on a button that has content_desc "shutter"
+- action 8: jade green touched on a selected button that has content_desc "shutter"
+- action 9: jade green touched on a button that has content_desc "shutter"
+- action 10: jade green waited for a loading state to finish
+- action 11: jade green touched on a selected button that has content_desc "shutter"
 - action 12: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "video"
-- action 2: touched on a button that has content-desc "shutter"
-- action 3: touched on a selected button that has content-desc "shutter"
-- action 4: touched on a button that has content-desc "shutter"
-- action 5: touched on a selected button that has content-desc "shutter"
-- action 6: touched on a button that has content-desc "shutter"
-- action 7: touched on a selected button that has content-desc "shutter"
-- action 8: touched on a button that has content-desc "shutter"
-- action 9: waited for a loading state to finish
-- action 10: touched on a selected button that has content-desc "shutter"
-- action 11: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: waited for a loading state to finish
-- action 2: touched on a button that has content-desc "view last captured media"
-- action 3: touched on a button that has content-desc "more options"
-- action 4: long touched on a button that has content-desc "more options"
-- action 5: touched on a button that has content-desc "view last captured media"
-- action 6: touched on a button that has content-desc "more options"
-- action 7: waited for a loading state to finish
+    <t>- action 1: jade green touched on a button that has content_desc "view last captured media"
+- action 3: jade green touched on a button that has content_desc "view last captured media"
+- action 5: jade green touched on a button that has content_desc "settings"
+- action 6: jade green touched on a button that has content_desc "back"
+- action 7: jade green touched on a button that has content_desc "view last captured media"
+- action 9: jade green touched on a button that has content_desc "view last captured media"
+- action 11: jade green touched on a button that has content_desc "view last captured media"
+- action 12: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "view last captured media"
+- action 2: jade green touched on a button that has content_desc "more options"
+- action 3: jade green touched on a button that has text "crop"
+- action 4: jade green touched on a button that has text "save"
+- action 6: jade green touched on a button that has content_desc "view last captured media"
+- action 7: jade green touched on a button that has content_desc "more options"
 - action 8: task completed?</t>
   </si>
   <si>
-    <t>- action 1: waited for a loading state to finish
-- action 2: touched on a button that has content-desc "view last captured media"
-- action 3: touched on a button that has content-desc "more options"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has content-desc "more options"
-- action 6: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "view last captured media"
-- action 8: touched on a button that has content-desc "more options"
-- action 9: touched on a button that has resource_id "android:id/expand_activities_button"
-- action 10: touched on a button that has resource_id "android:id/expand_activities_button"
-- action 11: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: waited for a loading state to finish
-- action 2: touched on a button that has content-desc "view last captured media"
-- action 3: touched on a button that has content-desc "more options"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has content-desc "more options"
-- action 6: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "share with print"
-- action 8: press the back button because you stayed on the pages not belonging to the target app for too long
-- action 9: touched on a button that has content-desc "view last captured media"
-- action 10: touched on a button that has content-desc "more options"
-- action 11: touched on a button that has content-desc "more options"
-- action 12: touched on a button that has content-desc "more options"
-- action 13: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 2: task completed?</t>
+    <t>- action 1: jade green waited for a loading state to finish
+- action 2: jade green touched on a button that has content_desc "view last captured media"
+- action 3: jade green touched on a button that has content_desc "more options"
+- action 4: jade green touched on a button that has content_desc "share with print"
+- action 5: jade green touched on a button that has content_desc "dcim, navigate up"
+- action 6: jade green touched on a button that has resource_id "android:id/expand_activities_button"
+- action 7: jade green touched on a button that has content_desc "dcim, navigate up"
+- action 8: task completed?</t>
+  </si>
+  <si>
+    <t>- action 2: jade green touched on a button that has text "camera"
+- action 3: jade green touched on a button that has content_desc "settings"
+- action 4: jade green touched on a button that has text "photo compression quality, 80%"
+- action 5: jade green touched on a button that has text "50%"
+- action 6: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "toggle front/back camera"
@@ -1266,17 +1248,20 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "video"
-- action 2: touched on a button that has content-desc "toggle front/back camera"
-- action 3: touched on a button that has content-desc "shutter"
-- action 4: touched on a selected button that has content-desc "shutter"
-- action 5: touched on a button that has content-desc "shutter"
-- action 6: touched on a selected button that has content-desc "shutter"
-- action 7: touched on a button that has content-desc "shutter"
-- action 8: touched on a selected button that has content-desc "shutter"
-- action 9: touched on a button that has content-desc "shutter"
-- action 10: touched on a selected button that has content-desc "shutter"
-- action 11: task completed?</t>
+    <t>- action 1: jade green touched on a button that has text "video"
+- action 2: jade green touched on a button that has content_desc "toggle front/back camera"
+- action 3: jade green touched on a button that has content_desc "shutter"
+- action 4: jade green touched on a selected button that has content_desc "shutter"
+- action 5: jade green touched on a button that has content_desc "shutter"
+- action 6: jade green touched on a selected button that has content_desc "shutter"
+- action 7: jade green touched on a button that has content_desc "shutter"
+- action 8: jade green touched on a selected button that has content_desc "shutter"
+- action 9: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 2: jade green touched on a checkbox that has text "use volume buttons as shutter"
+- action 3: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -1284,20 +1269,19 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 2: touched on a button that has text "always use same snooze time"
-- action 3: touched on a button that has text "snooze time, 10 minutes"
-- action 4: touched on a button that has text "5 minutes"
-- action 5: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 2: touched on a button that has content-desc "back"
-- action 3: touched on a button that has text "alarm"
-- action 4: touched on a button that has content-desc "sort by"
-- action 5: touched on a button that has text "day and alarm time"
-- action 6: touched on a button that has text "ok"
-- action 7: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 2: jade green touched on a button that has text "snooze time, 10 minutes"
+- action 3: jade green touched on a button that has text "5 minutes"
+- action 4: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 4: jade green touched on a button that has content_desc "back"
+- action 5: jade green touched on a button that has text "alarm"
+- action 6: jade green touched on a button that has content_desc "sort by"
+- action 7: jade green touched on a button that has text "day and alarm time"
+- action 8: jade green touched on a button that has text "ok"
+- action 9: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "new timer"
@@ -1341,9 +1325,9 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "alarm"
-- action 2: touched on a button that has text "7:00 am, mon, tue, wed, thu, fri"
-- action 3: touched on a checkbox that has text "vibrate"
+    <t>- action 1: jade green touched on a button that has text "alarm"
+- action 2: jade green touched on a button that has text "7:00 am, mon, tue, wed, thu, fri"
+- action 3: jade green touched on a checkbox that has text "vibrate"
 - action 4: task completed?</t>
   </si>
   <si>
@@ -1381,67 +1365,57 @@
 - action 6: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "allow"
-- action 2: touched on a button that has text "groups"
-- action 3: touched on a button that has text "create group"
-- action 4: filled a focused textfield that has text "title" with the text "classmates"
-- action 5: touched on a button that has text "ok"
-- action 6: touched on a button that has content-desc "create group"
-- action 7: touched on a button that has text "cancel"
-- action 8: touched on a button that has text "classmates (0)"
-- action 9: touched on a button that has text "add contacts"
-- action 10: touched on a checkbox that has resource_id "com.simplemobiletools.contacts.pro:id/contact_checkbox"
-- action 11: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "search"
-- action 2: filled a focused textfield that has text "search" with the text "bob"
-- action 3: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a checkbox that has text "show a dialpad button on the main screen"
-- action 4: touched on a checked checkbox that has text "show a dialpad button on the main screen"
+    <t>- action 1: jade green touched on a button that has text "groups"
+- action 2: jade green touched on a button that has content_desc "create group"
+- action 3: jade green filled a focused textfield that has text "title" with the text "classmates"
+- action 4: jade green touched on a button that has text "ok"
+- action 5: jade green touched on a button that has text "classmates (0)"
+- action 6: jade green touched on a button that has text "add contacts"
+- action 7: jade green touched on a checkbox that has resource_id "com.simplemobiletools.contacts.pro:id/contact_checkbox"
+- action 8: jade green touched on a checked checkbox that has resource_id "com.simplemobiletools.contacts.pro:id/contact_checkbox"
+- action 9: jade green touched on a checkbox that has resource_id "com.simplemobiletools.contacts.pro:id/contact_checkbox"
+- action 10: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "search"
+- action 2: jade green filled a focused textfield that has text "search" with the text "bob"
+- action 5: jade green touched on a button that has text "contacts"
+- action 6: jade green touched on a button that has text "bob"
+- action 7: jade green touched on a button that has content_desc "delete"
+- action 8: jade green touched on a button that has text "yes"
+- action 9: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 4: jade green touched on a checkbox that has text "show a dialpad button on the main screen"
+- action 5: jade green touched on a checked checkbox that has text "show a dialpad button on the main screen"
+- action 6: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "export contacts to a .vcf file"
+- action 3: jade green filled a textfield that has text "contacts_2025_02_16_10_46_03" with the text "classmate.vcf"
+- action 4: jade green touched on a button that has text "ok"
+- action 5: jade green filled a textfield that has text "classmate.vcf.vcf" with the text "classmate.vcf"
+- action 6: jade green touched on a button that has text "save"
+- action 7: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "search"
+- action 2: jade green filled a focused textfield that has text "search" with the text "bob"
+- action 4: jade green filled a focused textfield that has text "bob" with the text ""
+- action 6: jade green filled a focused textfield that has text "bob" with the text ""
+- action 7: jade green touched on a button that has text "favorites"
+- action 8: jade green touched on a button that has text "contacts"
+- action 9: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "dialpad"
+- action 3: jade green filled a focused textfield that has resource_id "com.simplemobiletools.dialer:id/dialpad_input" with the text "911"
+- action 4: jade green touched on a button that has content_desc "call number"
 - action 5: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "export contacts to a .vcf file"
-- action 3: filled a textfield that has text "contacts_2024_10_26_08_09_49" with the text "classmate.vcf"
-- action 4: touched on a button that has text "ok"
-- action 5: filled a textfield that has text "classmate.vcf.vcf" with the text "classmate.vcf"
-- action 6: touched on a button that has text "save"
-- action 7: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has text "bob"
-- action 2: touched on a button that has content-desc "call contact"
-- action 3: touched on a button that has text "allow"
-- action 4: touched on a button that has content-desc "call contact"
-- action 5: touched on a button that has content-desc "call contact"
-- action 6: touched on a button that has content-desc "call contact"
-- action 7: touched on a button that has text "app info"
-- action 8: touched on a button that has content-desc "call contact"
-- action 9: touched on a button that has content-desc "more options"
-- action 10: touched on a button that has text "open with"
-- action 11: touched on a button that has text "contacts, details"
-- action 12: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "dialpad"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has text "dialpad"
-- action 7: touched on a button that has content-desc "more options"
-- action 8: touched on a button that has text "dialpad"
-- action 10: touched on a button that has content-desc "create new contact"
-- action 12: touched on a button that has content-desc "more options"
-- action 13: touched on a button that has text "dialpad"
-- action 15: touched on a button that has content-desc "more options"
-- action 16: touched on a button that has text "dialpad"
-- action 18: touched on a button that has content-desc "sort by"
-- action 19: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "bob"
@@ -1451,21 +1425,16 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has content-desc "more options"
-- action 3: touched on a button that has text "contacts"
-- action 4: touched on a button that has content-desc "sort by"
-- action 5: touched on a button that has text "date created"
-- action 6: touched on a button that has text "descending"
-- action 7: touched on a button that has text "ok"
-- action 8: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 2: touched on a button that has text "manage shown contact fields"
-- action 3: touched on a button that has text "ok"
-- action 4: touched on a button that has text "manage shown contact fields"
-- action 5: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "sort by"
+- action 2: jade green touched on a button that has text "date created"
+- action 3: jade green touched on a button that has text "descending"
+- action 4: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: jade green touched on a button that has text "manage shown contact fields"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "edit"
@@ -1483,21 +1452,28 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a button that has text "customize colors"
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: jade green touched on a button that has text "customize colors"
+- action 4: jade green touched on a button that has text "theme, dark"
+- action 5: jade green touched on a button that has text "ok"
+- action 6: jade green touched on a button that has text "light"
+- action 7: jade green touched on a button that has content_desc "save"
+- action 8: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "remove from favorites"
+- action 2: jade green touched on a button that has text "alice"
+- action 3: jade green touched on a button that has content_desc "add to favorites"
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "remove from favorites"
-- action 2: touched on a button that has text "alice"
-- action 3: touched on a button that has content-desc "add to favorites"
-- action 4: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "click to return to previous screen"
+- action 2: jade green touched on a button that has content_desc "more options"
+- action 3: jade green touched on a button that has text "settings"
+- action 4: jade green touched on a button that has text "font size, large"
+- action 5: jade green touched on a button that has text "medium"
+- action 6: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "dialpad"
@@ -1506,18 +1482,9 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "alice"
-- action 2: touched on a button that has text "1 (234) 567-890, mobile"
-- action 3: touched on a button that has text "alice"
-- action 4: touched on a button that has text "1 (234) 567-890, mobile"
-- action 5: touched on a button that has text "alice"
-- action 6: touched on a button that has text "1 (234) 567-890, mobile"
-- action 7: touched on a button that has text "call history"
-- action 8: long touched on a button that has text "alice (3), 03:18 pm"
-- action 9: touched on a button that has content-desc "delete"
-- action 10: touched on a button that has text "no"
-- action 11: touched on a button that has text "contacts"
-- action 12: task completed?</t>
+    <t>- action 1: jade green touched on a button that has text "alice"
+- action 2: jade green touched on a button that has text "1 (234) 567-890, mobile"
+- action 3: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "create new contact"
@@ -1541,6 +1508,14 @@
 - action 4: task completed?</t>
   </si>
   <si>
+    <t>- action 1: jade green touched on a button that has text "call history"
+- action 2: jade green touched on a button that has content_desc "search"
+- action 3: jade green filled a focused textfield that has text "search" with the text "bob"
+- action 4: jade green touched on a button that has content_desc "filter"
+- action 5: jade green touched on a button that has text "ok"
+- action 6: task completed?</t>
+  </si>
+  <si>
     <t>- action 2: touched on a button that has text "alice"
 - action 3: task completed?</t>
   </si>
@@ -1553,20 +1528,20 @@
 - action 6: task completed?</t>
   </si>
   <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: task completed?</t>
+  </si>
+  <si>
     <t>- action 1: touched on a button that has text "favorites"
 - action 2: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "search"
-- action 2: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 3: touched on a button that has content-desc "back"
-- action 4: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 5: touched on a button that has content-desc "back"
-- action 6: touched on a button that has text "files"
-- action 7: long touched on a button that has text "alarms, 0 items"
-- action 8: touched on a button that has content-desc "add to favorites"
-- action 9: touched on a button that has text "ok"
-- action 10: task completed?</t>
+    <t>- action 2: jade green touched on a button that has content_desc "settings"
+- action 3: jade green touched on a button that has text "manage favorites"
+- action 4: jade green touched on a button that has content_desc "add favorites"
+- action 5: jade green touched on a button that has text "alarms_new, 0 items"
+- action 6: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -1581,13 +1556,14 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 14: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 2: touched on a button that has text "customize colors"
-- action 3: touched on a button that has text "theme, light"
+    <t>- action 1: jade green touched on a button that has resource_id "com.simplemobiletools.filemanager.pro:id/expand_button"
+- action 2: jade green touched on a button that has text "sd card, 835.5 mb, free[...and more]"
+- action 3: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 2: jade green touched on a button that has text "customize colors"
+- action 3: jade green touched on a button that has text "theme, light"
 - action 4: task completed?</t>
   </si>
   <si>
@@ -1615,10 +1591,11 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "recents"
-- action 2: touched on a textfield that has text "search"
-- action 3: filled a focused textfield that has text "search" with the text "video2.mp4"
-- action 4: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "back"
+- action 2: jade green touched on a button that has text "recents"
+- action 7: jade green touched on a button that has content_desc "search"
+- action 8: jade green filled a focused textfield that has text "search" with the text "video2.mp4"
+- action 9: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "recents"
@@ -1638,18 +1615,10 @@
 - action 6: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "search"
-- action 2: filled a focused textfield that has text "search" with the text "screen_2023-06-30_141247.png"
-- action 3: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 4: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 5: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 6: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 7: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 8: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 9: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 10: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 11: touched on a button that has text "internal, 4.8 gb, free[...and more]"
-- action 12: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "search"
+- action 2: jade green filled a focused textfield that has text "search" with the text "screen_2023-06-30_141247.png"
+- action 3: jade green touched on a button that has text "internal, 4.8 gb, free[...and more]"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "sort by"
@@ -1665,20 +1634,16 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 2: touched on a checkbox that has text "show hidden items"
-- action 3: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "change view type"
-- action 3: touched on a button that has text "ok"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has text "change view type"
-- action 6: touched on a button that has text "grid"
-- action 7: touched on a button that has text "list"
-- action 8: touched on a button that has text "ok"
-- action 9: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 2: jade green touched on a checked checkbox that has text "show hidden items"
+- action 3: jade green touched on a checkbox that has text "show hidden items"
+- action 4: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "change view type"
+- action 3: jade green touched on a button that has text "list"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "column count"
@@ -1686,11 +1651,10 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 9: touched on a checked checkbox that has text "gifs"
-- action 10: touched on a button that has text "ok"
-- action 11: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 9: jade green touched on a button that has content_desc "more options"
+- action 10: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "dcim, 53, /storage/emulated/0/"
@@ -1703,16 +1667,18 @@
 - action 4: task completed?</t>
   </si>
   <si>
+    <t>- action 1: jade green touched on a button that has text "dcim, 87"
+- action 2: task completed?</t>
+  </si>
+  <si>
     <t>- action 1: touched on a button that has content-desc "show all folders content"
 - action 2: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "switch to folder view"
-- action 2: touched on a button that has content-desc "more options"
-- action 3: touched on a button that has text "sort by"
-- action 4: touched on a button that has text "name"
-- action 5: touched on a button that has text "ok"
-- action 6: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "sort by"
+- action 3: jade green touched on a button that has text "name"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "dcim, 53"
@@ -1723,12 +1689,9 @@
 - action 6: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a textfield that has text "search"
-- action 2: filled a focused textfield that has text "search" with the text "bob"
-- action 3: long touched on a button that has text "mydearalice, draft, hi alice, this is a test message to see how the mm[...][...and more]"
-- action 4: touched on a button that has content-desc "delete"
-- action 5: touched on a button that has text "yes"
-- action 6: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "search"
+- action 2: jade green filled a focused textfield that has text "search" with the text "bob"
+- action 3: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -1749,12 +1712,11 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "settings"
-- action 2: touched on a button that has content-desc "settings"
-- action 3: touched on a button that has text "show a character counter at writing messages"
-- action 4: touched on a button that has text "show a character counter at writing messages"
-- action 5: touched on a button that has text "show a character counter at writing messages"
-- action 6: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 3: jade green touched on a button that has text "send long messages as mms"
+- action 7: jade green touched on a button that has content_desc "settings"
+- action 8: jade green touched on a button that has text "show a character counter at writing messages"
+- action 12: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "alice, i love you, 09.09"
@@ -1763,19 +1725,10 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "start a conversation"
-- action 2: touched on a button that has text "alice, 1234567890"
-- action 3: filled a focused textfield that has text "type a messageâ€¦" with the text "hi alice, i wanted to share some exciting news with you! i've been working on a new project that combines technology and art, and it's finally coming together. it's been a long journey, but seeing the pieces fall into place is truly rewarding. i'll send you some images soon!"
-- action 4: touched on a button that has content-desc "attachment"
-- action 5: touched on a button that has text "choose photo"
-- action 6: touched on a button that has text "large files"
-- action 7: touched on a button that has content-desc "show roots"
-- action 8: touched on a button that has text "images"
-- action 9: touched on a button that has text "dcim"
-- action 10: touched on a button that has text "dcim"
-- action 11: press the back button because you stayed on the pages not belonging to the target app for too long
-- action 12: touched on a button that has text "choose photo"
-- action 13: task completed?</t>
+    <t>- action 1: jade green touched on a button that has text "team_discussion, hi alice, i hope you’re doing well! i wanted to sh[...], 07:44 pm"
+- action 2: jade green filled a textfield that has text "type a message…" with the text "hi alice, i hope you're doing well! i wanted to share some exciting updates with you. over the past few weeks, i've been working on a new project that has really taken off. it's been a lot of work, but i'm thrilled with the progress we've made. how have you been? looking forward to hearing from you!"
+- action 3: jade green touched on a button that has text "mms"
+- action 4: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -1783,31 +1736,17 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "mydearalice, draft, hi alice, this is a test message to see how the mm[...][...and more]"
-- action 2: touched on a button that has content-desc "dial number"
-- action 3: long touched on a button that has content-desc "more options"
-- action 4: touched on a button that has content-desc "more options"
-- action 5: touched on a button that has text "conversation details"
-- action 6: long touched on a button that has text "alice, 1234567890"
-- action 7: touched on a button that has text "1 (234) 567-890, mobile"
-- action 8: long touched on a button that has text "alice, 1234567890"
-- action 9: touched on a button that has text "1 (234) 567-890, mobile"
-- action 10: touched on a button that has text "close app"
-- action 11: long touched on a button that has text "alice, 1234567890"
-- action 12: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: long touched on a button that has text "alice, i love you, 09.09"
-- action 2: touched on a button that has content-desc "more options"
-- action 4: long touched on a selected button that has text "alice, i love you, 09.09"
-- action 5: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "more options"
-- action 8: touched on a button that has text "archive"
-- action 9: touched on a button that has text "no"
-- action 10: long touched on a button that has content-desc "more options"
-- action 11: touched on a button that has content-desc "more options"
-- action 13: touched on a button that has content-desc "more options"
-- action 14: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "settings"
+- action 2: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has text "team_discussion, hi alice, i hope you’re doing well! i wanted to sh[...], 07:49 pm"
+- action 2: jade green touched on a button that has content_desc "dial number"
+- action 3: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "click to return to previous screen"
+- action 2: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has text "alice, draft, hi alice, this is a test message to see how the mm[...][...and more]"
@@ -1838,30 +1777,15 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has text "test1, &lt;unknown&gt; â€¢ recordings, 00:01"
-- action 2: touched on a button that has content-desc "repeat current song"
-- action 3: touched on a button that has text "test1, &lt;unknown&gt; â€¢ recordings, 00:01"
-- action 4: touched on a button
-- action 5: touched on a button that has text "test1, &lt;unknown&gt; â€¢ recordings, 00:01"
-- action 6: touched on a button that has content-desc "stop playback after current song"
-- action 7: touched on a button that has content-desc "repeat off"
-- action 8: touched on a button that has content-desc "repeat all"
-- action 9: touched on a button that has content-desc "play / pause"
-- action 10: touched on a button that has content-desc "previous"
-- action 11: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has text "tracks"
-- action 2: touched on a button that has text "test1, &lt;unknown&gt; â€¢ recordings, 00:01"
-- action 3: touched on a button that has content-desc "play / pause"
-- action 4: touched on a button that has content-desc "disable shuffle"
-- action 5: touched on a button that has text "test1, &lt;unknown&gt; â€¢ recordings, 00:01"
-- action 6: touched on a button that has content-desc "enable shuffle"
-- action 7: touched on a button that has content-desc "disable shuffle"
-- action 8: touched on a button that has content-desc "enable shuffle"
-- action 9: touched on a button that has content-desc "previous"
-- action 10: touched on a button that has content-desc "play / pause"
-- action 11: task completed?</t>
+    <t>- action 1: jade green touched on a button that has text "test1, &lt;unknown&gt; • recordings, 00:01"
+- action 2: jade green touched on a button that has content_desc "play / pause"
+- action 3: jade green touched on a button that has content_desc "repeat current song"
+- action 4: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has text "test1, &lt;unknown&gt; • recordings, 00:01"
+- action 2: jade green touched on a button that has content_desc "play / pause"
+- action 3: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "more options"
@@ -1870,20 +1794,18 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a checkbox that has text "gapless playback"
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: jade green touched on a checkbox that has text "gapless playback"
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "sort by"
-- action 2: touched on a button that has text "date added"
-- action 3: touched on a button that has text "track number"
-- action 4: touched on a button that has text "duration"
-- action 5: touched on a button that has text "date added"
-- action 6: touched on a button that has text "title"
-- action 7: touched on a button that has text "descending"
-- action 8: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "back"
+- action 2: jade green touched on a button that has content_desc "sort by"
+- action 3: jade green touched on a button that has text "date added"
+- action 4: jade green touched on a button that has text "descending"
+- action 5: jade green touched on a button that has text "ok"
+- action 6: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "create a new note"
@@ -1903,13 +1825,14 @@
 - action 7: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "create a new note"
-- action 2: filled a focused textfield that has text "label" with the text "test"
-- action 3: touched on a button that has text "ok"
-- action 4: filled a focused textfield that has text "test" with the text "12345678"
-- action 6: touched on a focused textfield that has text "12345678"
-- action 9: touched on a button that has content-desc "search"
-- action 10: filled a focused textfield that has text "search" with the text "234"
+    <t>- action 1: jade green touched on a button that has content_desc "create a new note"
+- action 2: jade green filled a focused textfield that has text "label" with the text "test"
+- action 3: jade green touched on a button that has text "text note"
+- action 4: jade green filled a focused textfield that has text "test" with the text "12345678"
+- action 5: jade green touched on a button that has text "ok"
+- action 7: jade green filled a focused textfield that has text "12345678" with the text "test1"
+- action 8: jade green touched on a button that has text "ok"
+- action 9: jade green filled a focused textfield that has text "test1" with the text "test_unique"
 - action 11: task completed?</t>
   </si>
   <si>
@@ -1934,29 +1857,29 @@
 - action 5: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 3: touched on a button that has resource_id "com.simplemobiletools.notes.pro:id/settings_gravity_holder"
-- action 4: touched on a button that has content-desc "open note"
-- action 5: touched on a button that has text "center alignment note"
-- action 6: touched on a button that has content-desc "more options"
-- action 7: touched on a button that has content-desc "open note"
-- action 8: touched on a button that has text "center alignment note"
-- action 9: touched on a button that has content-desc "more options"
-- action 10: touched on a button that has text "rename note"
-- action 11: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "create a new note"
-- action 2: filled a focused textfield that has text "label" with the text "test"
-- action 3: touched on a button that has text "ok"
-- action 4: filled a focused textfield that has text "test" with the text "test 2"
-- action 5: touched on a button that has text "ok"
-- action 6: touched on a button that has text "add new checklist items"
-- action 7: filled a focused textfield that has resource_id "com.simplemobiletools.notes.pro:id/title_edit_text" with the text "item 1"
-- action 8: touched on a button that has resource_id "com.simplemobiletools.notes.pro:id/add_item"
-- action 9: filled a focused textfield that has resource_id "com.simplemobiletools.notes.pro:id/title_edit_text" with the text "item 2"
-- action 10: task completed?</t>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: jade green touched on a button that has resource_id "com.simplemobiletools.notes.pro:id/settings_gravity_holder"
+- action 4: jade green touched on a button that has content_desc "open note"
+- action 5: jade green touched on a button that has text "center alignment note"
+- action 6: jade green touched on a button that has content_desc "more options"
+- action 8: jade green touched on a button that has content_desc "open note"
+- action 9: jade green touched on a button that has text "center alignment note"
+- action 10: jade green touched on a button that has content_desc "more options"
+- action 12: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "create a new note"
+- action 2: jade green filled a focused textfield that has text "label" with the text "test"
+- action 3: jade green touched on a button that has text "ok"
+- action 4: jade green filled a focused textfield that has text "test" with the text "test1"
+- action 5: jade green touched on a button that has text "ok"
+- action 6: jade green filled a focused textfield that has text "test1" with the text "test2"
+- action 7: jade green filled a focused textfield that has text "test2" with the text "test_new"
+- action 8: jade green touched on a button that has text "ok"
+- action 9: jade green touched on a button that has content_desc "more options"
+- action 11: jade green touched on a button that has text "add new checklist items"
+- action 12: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "more options"
@@ -1965,30 +1888,27 @@
 - action 4: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "open note"
-- action 2: touched on a button that has text "diary"
-- action 3: touched on a button that has text "general note"
-- action 4: touched on a button that has text "diary"
-- action 5: touched on a button that has content-desc "more options"
-- action 6: touched on a button that has text "export as file"
-- action 7: filled a textfield that has text "diary.txt" with the text "diary.txt"
-- action 8: touched on a button that has text "save"
-- action 9: touched on a button that has text "only export the current file content
-- action 11: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "open note"
-- action 2: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has content-desc "more options"
-- action 2: touched on a button that has text "settings"
-- action 4: touched on a button that has text "customize colors"
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "export as file"
+- action 3: jade green filled a textfield that has text "test_unique_3.txt" with the text "diary.txt"
+- action 4: jade green touched on a button that has text "save"
+- action 5: jade green touched on a button that has text "only export the current file content
+- action 6: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "print"
+- action 3: jade green touched on a button that has content_desc "save to pdf"
+- action 4: jade green filled a textfield that has text "test_unique_3" with the text "diary.pdf"
+- action 5: jade green touched on a button that has text "save"
+- action 6: task completed?</t>
+  </si>
+  <si>
+    <t>- action 1: jade green touched on a button that has content_desc "more options"
+- action 2: jade green touched on a button that has text "settings"
+- action 3: jade green touched on a button that has text "customize colors"
+- action 4: jade green touched on a button that has text "theme, light"
 - action 5: task completed?</t>
-  </si>
-  <si>
-    <t>- action 1: touched on a button that has text "word count note"
-- action 2: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -2009,12 +1929,15 @@
 - action 3: task completed?</t>
   </si>
   <si>
-    <t>- action 1: touched on a button that has content-desc "search"
-- action 2: filled a focused textfield that has text "search" with the text "test1"
-- action 3: touched on a button that has text "test1 (2).m4a, 00:01, 26.10.2024, 11:32 pm[...and more]"
-- action 4: filled a focused textfield that has text "test1" with the text "test1.m4a"
-- action 5: filled a focused textfield that has text "test1.m4a" with the text "test1"
-- action 6: task completed?</t>
+    <t>- action 1: jade green touched on a button that has text "while using the app"
+- action 2: jade green touched on a button that has content_desc "search"
+- action 3: jade green filled a focused textfield that has text "search" with the text "test1"
+- action 4: jade green touched on a button that has content_desc "settings"
+- action 5: jade green touched on a button that has content_desc "back"
+- action 6: jade green touched on a button that has text "recycle bin"
+- action 7: jade green touched on a button that has content_desc "search"
+- action 8: jade green filled a focused textfield that has text "search" with the text "test1"
+- action 9: task completed?</t>
   </si>
   <si>
     <t>- action 1: touched on a button that has content-desc "settings"
@@ -2064,8 +1987,13 @@
     <t>True
 True
 True
-False
-False</t>
+True
+True
+True
+True
+True
+True
+True</t>
   </si>
   <si>
     <t>False
@@ -2080,64 +2008,11 @@
   </si>
   <si>
     <t>True
-False
-True
-False
-False
-True
-True
-True
-False</t>
-  </si>
-  <si>
-    <t>True
-True
-False
-False
-False
-False</t>
-  </si>
-  <si>
-    <t>True
 True
 True
 True
 True
 True
-True</t>
-  </si>
-  <si>
-    <t>False
-False
-True
-True
-False
-False
-False
-False
-False</t>
-  </si>
-  <si>
-    <t>True
-True
-True</t>
-  </si>
-  <si>
-    <t>True
-False
-True
-True
-True</t>
-  </si>
-  <si>
-    <t>False
-False
-False
-False
-False
-False
-False
-False
 False
 False</t>
   </si>
@@ -2156,7 +2031,40 @@
   </si>
   <si>
     <t>True
+True
+True
+True
+True
+True
+True</t>
+  </si>
+  <si>
+    <t>True
+True
+True</t>
+  </si>
+  <si>
+    <t>True
+True
+True
+True
+True
+True</t>
+  </si>
+  <si>
+    <t>True
+True
 False
+False
+False
+False
+False
+False
+True
+False</t>
+  </si>
+  <si>
+    <t>True
 False
 False
 False
@@ -2168,28 +2076,17 @@
   </si>
   <si>
     <t>True
-False
-False
-False
-False
+True
 False
 False</t>
   </si>
   <si>
-    <t>False
-True
-False
+    <t>True
 False
 False</t>
   </si>
   <si>
-    <t>True
-False
-False
-False</t>
-  </si>
-  <si>
-    <t>True
+    <t>False
 True
 False
 False
@@ -2197,17 +2094,10 @@
 False
 False
 False
-False
 False</t>
   </si>
   <si>
     <t>True
-True</t>
-  </si>
-  <si>
-    <t>True
-True
-True
 True
 True
 True
@@ -2215,8 +2105,11 @@
 False
 False
 False
-False
 False</t>
+  </si>
+  <si>
+    <t>True
+True</t>
   </si>
   <si>
     <t>True
@@ -2233,21 +2126,6 @@
   </si>
   <si>
     <t>True
-True
-False
-False
-False
-False
-False
-False</t>
-  </si>
-  <si>
-    <t>False
-False
-False
-False
-False
-False
 False
 False
 False
@@ -2258,6 +2136,11 @@
   </si>
   <si>
     <t>True
+True
+True
+True
+False
+False
 False</t>
   </si>
   <si>
@@ -2269,16 +2152,7 @@
 False
 False
 False
-False
-False
 True</t>
-  </si>
-  <si>
-    <t>True
-True
-True
-True
-False</t>
   </si>
   <si>
     <t>False
@@ -2301,41 +2175,98 @@
 True
 True
 True
+True
+False
+False
+False
+False</t>
+  </si>
+  <si>
+    <t>False
+False
+False
+True
+True
+True
 True</t>
   </si>
   <si>
     <t>False
+False
+True
+False
+False
+False
+False</t>
+  </si>
+  <si>
+    <t>False
+True
+True
+True</t>
+  </si>
+  <si>
+    <t>True
+True
+False</t>
+  </si>
+  <si>
+    <t>False
+False
+False</t>
+  </si>
+  <si>
+    <t>True
+True
+False
+False
+False</t>
+  </si>
+  <si>
+    <t>True
+False
+False
+False</t>
+  </si>
+  <si>
+    <t>True
+False
+False
+False
+False</t>
+  </si>
+  <si>
+    <t>False
+False
+True
+False</t>
+  </si>
+  <si>
+    <t>True
+False</t>
+  </si>
+  <si>
+    <t>False
+False</t>
+  </si>
+  <si>
+    <t>True
+True
+False
+True
+True
+False</t>
+  </si>
+  <si>
+    <t>True
 True
 True
 True
 True
 False
 False
-True
-True
 False
 False</t>
-  </si>
-  <si>
-    <t>False
-False
-False</t>
-  </si>
-  <si>
-    <t>True
-True
-True
-False
-True</t>
-  </si>
-  <si>
-    <t>True
-True
-False
-True
-True
-True
-True</t>
   </si>
   <si>
     <t>True
@@ -2347,160 +2278,7 @@
 False
 False
 False
-False
-False
-True</t>
-  </si>
-  <si>
-    <t>False
-True
-False
-False
-False
-False
-False
-False
-False
-False
-False
-False
 False</t>
-  </si>
-  <si>
-    <t>False
-False
-False
-True
-True
-True
-True
-True</t>
-  </si>
-  <si>
-    <t>False
-True
-True
-True</t>
-  </si>
-  <si>
-    <t>True
-True
-False</t>
-  </si>
-  <si>
-    <t>False
-False</t>
-  </si>
-  <si>
-    <t>False
-False
-False
-False
-False
-False
-False
-False
-False
-False
-False
-False</t>
-  </si>
-  <si>
-    <t>True
-True
-True
-False
-False
-False
-True
-True
-True</t>
-  </si>
-  <si>
-    <t>False
-True
-True
-True
-True
-True</t>
-  </si>
-  <si>
-    <t>False
-False
-False
-True
-True
-True</t>
-  </si>
-  <si>
-    <t>True
-False
-False
-False
-False
-False</t>
-  </si>
-  <si>
-    <t>True
-True
-False
-True
-True
-False
-False
-True
-True
-True
-False</t>
-  </si>
-  <si>
-    <t>False
-True
-False
-False
-False
-False
-False
-True
-False
-False
-True</t>
-  </si>
-  <si>
-    <t>True
-True
-False
-False
-False
-False
-False
-False
-False
-False
-True</t>
-  </si>
-  <si>
-    <t>True
-False
-False
-False
-False
-False
-True
-False</t>
-  </si>
-  <si>
-    <t>True
-True
-False
-False
-True
-False
-False
-False
-False
-False
-True</t>
   </si>
   <si>
     <t>True
@@ -2511,26 +2289,25 @@
 False
 False
 False
+True
 False
 False</t>
-  </si>
-  <si>
-    <t>False
-False
-True
-True
-True
-True
-True
-True
-True
-True</t>
   </si>
   <si>
     <t>True
 True
 True
 True
+False</t>
+  </si>
+  <si>
+    <t>True
+True
+False
+False
+False
+False
+False
 False
 False</t>
   </si>
@@ -3862,7 +3639,7 @@
         <v>318</v>
       </c>
       <c r="E2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -3871,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>511</v>
+        <v>504</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -3906,7 +3683,7 @@
         <v>319</v>
       </c>
       <c r="E3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -3915,7 +3692,7 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
@@ -3950,7 +3727,7 @@
         <v>320</v>
       </c>
       <c r="E4" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -3959,7 +3736,7 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>513</v>
+        <v>506</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -3994,7 +3771,7 @@
         <v>321</v>
       </c>
       <c r="E5" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -4003,7 +3780,7 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -4038,7 +3815,7 @@
         <v>322</v>
       </c>
       <c r="E6" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -4047,7 +3824,7 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
@@ -4082,7 +3859,7 @@
         <v>323</v>
       </c>
       <c r="E7" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -4091,7 +3868,7 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -4126,34 +3903,34 @@
         <v>324</v>
       </c>
       <c r="E8" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>517</v>
+        <v>510</v>
       </c>
       <c r="I8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="N8">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4170,7 +3947,7 @@
         <v>325</v>
       </c>
       <c r="E9" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -4179,7 +3956,7 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>518</v>
+        <v>511</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -4214,7 +3991,7 @@
         <v>326</v>
       </c>
       <c r="E10" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -4223,7 +4000,7 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>519</v>
+        <v>512</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -4258,7 +4035,7 @@
         <v>327</v>
       </c>
       <c r="E11" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -4267,7 +4044,7 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>520</v>
+        <v>513</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -4302,7 +4079,7 @@
         <v>328</v>
       </c>
       <c r="E12" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F12" t="b">
         <v>0</v>
@@ -4311,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>521</v>
+        <v>514</v>
       </c>
       <c r="I12" t="b">
         <v>0</v>
@@ -4346,7 +4123,7 @@
         <v>329</v>
       </c>
       <c r="E13" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="F13" t="b">
         <v>0</v>
@@ -4355,25 +4132,25 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>522</v>
+        <v>515</v>
       </c>
       <c r="I13" t="b">
         <v>0</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M13">
-        <v>0.5555555555555556</v>
+        <v>0.75</v>
       </c>
       <c r="N13">
-        <v>0.1111111111111111</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -4390,7 +4167,7 @@
         <v>330</v>
       </c>
       <c r="E14" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F14" t="b">
         <v>0</v>
@@ -4399,7 +4176,7 @@
         <v>0</v>
       </c>
       <c r="H14" t="s">
-        <v>523</v>
+        <v>516</v>
       </c>
       <c r="I14" t="b">
         <v>0</v>
@@ -4411,13 +4188,13 @@
         <v>2</v>
       </c>
       <c r="L14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="M14">
-        <v>0.3333333333333333</v>
+        <v>0.1818181818181818</v>
       </c>
       <c r="N14">
-        <v>0.3333333333333333</v>
+        <v>0.1818181818181818</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4434,7 +4211,7 @@
         <v>331</v>
       </c>
       <c r="E15" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -4443,7 +4220,7 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>524</v>
+        <v>517</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -4478,34 +4255,34 @@
         <v>332</v>
       </c>
       <c r="E16" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="s">
-        <v>525</v>
+        <v>518</v>
       </c>
       <c r="I16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="b">
         <v>0</v>
       </c>
       <c r="K16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L16">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M16">
-        <v>0.2222222222222222</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -4522,7 +4299,7 @@
         <v>333</v>
       </c>
       <c r="E17" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -4531,7 +4308,7 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -4566,16 +4343,16 @@
         <v>334</v>
       </c>
       <c r="E18" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
       </c>
       <c r="G18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -4587,13 +4364,13 @@
         <v>4</v>
       </c>
       <c r="L18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M18">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N18">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -4610,34 +4387,34 @@
         <v>335</v>
       </c>
       <c r="E19" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="F19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H19" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="I19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19" t="b">
         <v>0</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L19">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -4654,7 +4431,7 @@
         <v>336</v>
       </c>
       <c r="E20" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="F20" t="b">
         <v>0</v>
@@ -4663,25 +4440,25 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="I20" t="b">
         <v>0</v>
       </c>
       <c r="J20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L20">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>0.1818181818181818</v>
+        <v>0.3</v>
       </c>
       <c r="N20">
-        <v>0.1818181818181818</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -4698,7 +4475,7 @@
         <v>337</v>
       </c>
       <c r="E21" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -4707,7 +4484,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
@@ -4742,7 +4519,7 @@
         <v>338</v>
       </c>
       <c r="E22" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="F22" t="b">
         <v>0</v>
@@ -4751,7 +4528,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="I22" t="b">
         <v>0</v>
@@ -4763,13 +4540,13 @@
         <v>1</v>
       </c>
       <c r="L22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M22">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N22">
-        <v>0.1</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="23" spans="1:14">
@@ -4786,7 +4563,7 @@
         <v>339</v>
       </c>
       <c r="E23" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -4795,7 +4572,7 @@
         <v>1</v>
       </c>
       <c r="H23" t="s">
-        <v>532</v>
+        <v>525</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
@@ -4830,7 +4607,7 @@
         <v>340</v>
       </c>
       <c r="E24" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F24" t="b">
         <v>0</v>
@@ -4839,7 +4616,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>533</v>
+        <v>526</v>
       </c>
       <c r="I24" t="b">
         <v>0</v>
@@ -4848,16 +4625,16 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L24">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="M24">
-        <v>0.1428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="N24">
-        <v>0.1428571428571428</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="25" spans="1:14">
@@ -4874,7 +4651,7 @@
         <v>341</v>
       </c>
       <c r="E25" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="F25" t="b">
         <v>0</v>
@@ -4883,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="I25" t="b">
         <v>0</v>
@@ -4895,13 +4672,13 @@
         <v>1</v>
       </c>
       <c r="L25">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M25">
-        <v>0.2</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="26" spans="1:14">
@@ -4918,7 +4695,7 @@
         <v>342</v>
       </c>
       <c r="E26" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -4927,7 +4704,7 @@
         <v>1</v>
       </c>
       <c r="H26" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
       <c r="I26" t="b">
         <v>1</v>
@@ -4962,7 +4739,7 @@
         <v>343</v>
       </c>
       <c r="E27" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="F27" t="b">
         <v>0</v>
@@ -4971,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="I27" t="b">
         <v>0</v>
@@ -4983,13 +4760,13 @@
         <v>1</v>
       </c>
       <c r="L27">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>0.25</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N27">
-        <v>0.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:14">
@@ -5006,7 +4783,7 @@
         <v>344</v>
       </c>
       <c r="E28" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="F28" t="b">
         <v>0</v>
@@ -5015,7 +4792,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="I28" t="b">
         <v>0</v>
@@ -5024,16 +4801,16 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>0.2</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="N28">
-        <v>0.2</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="29" spans="1:14">
@@ -5050,7 +4827,7 @@
         <v>345</v>
       </c>
       <c r="E29" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -5059,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="H29" t="s">
-        <v>538</v>
+        <v>531</v>
       </c>
       <c r="I29" t="b">
         <v>1</v>
@@ -5094,34 +4871,34 @@
         <v>346</v>
       </c>
       <c r="E30" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
       <c r="F30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H30" t="s">
-        <v>539</v>
+        <v>532</v>
       </c>
       <c r="I30" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30" t="b">
         <v>0</v>
       </c>
       <c r="K30">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L30">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N30">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -5138,7 +4915,7 @@
         <v>347</v>
       </c>
       <c r="E31" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -5147,7 +4924,7 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>540</v>
+        <v>533</v>
       </c>
       <c r="I31" t="b">
         <v>0</v>
@@ -5182,7 +4959,7 @@
         <v>348</v>
       </c>
       <c r="E32" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F32" t="b">
         <v>0</v>
@@ -5191,7 +4968,7 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>541</v>
+        <v>534</v>
       </c>
       <c r="I32" t="b">
         <v>0</v>
@@ -5200,16 +4977,16 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L32">
         <v>8</v>
       </c>
       <c r="M32">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="N32">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -5226,7 +5003,7 @@
         <v>349</v>
       </c>
       <c r="E33" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="F33" t="b">
         <v>0</v>
@@ -5235,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>542</v>
+        <v>535</v>
       </c>
       <c r="I33" t="b">
         <v>0</v>
@@ -5244,16 +5021,16 @@
         <v>0</v>
       </c>
       <c r="K33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L33">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M33">
-        <v>0.1818181818181818</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N33">
-        <v>0.1818181818181818</v>
+        <v>0.5714285714285714</v>
       </c>
     </row>
     <row r="34" spans="1:14">
@@ -5279,7 +5056,7 @@
         <v>0</v>
       </c>
       <c r="H34" t="s">
-        <v>543</v>
+        <v>536</v>
       </c>
       <c r="I34" t="b">
         <v>0</v>
@@ -5288,16 +5065,16 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>0.125</v>
       </c>
     </row>
     <row r="35" spans="1:14">
@@ -5314,34 +5091,34 @@
         <v>351</v>
       </c>
       <c r="E35" t="s">
-        <v>482</v>
+        <v>465</v>
       </c>
       <c r="F35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H35" t="s">
-        <v>544</v>
+        <v>537</v>
       </c>
       <c r="I35" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L35">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:14">
@@ -5358,7 +5135,7 @@
         <v>352</v>
       </c>
       <c r="E36" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -5367,7 +5144,7 @@
         <v>1</v>
       </c>
       <c r="H36" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -5411,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="I37" t="b">
         <v>0</v>
@@ -5423,13 +5200,13 @@
         <v>5</v>
       </c>
       <c r="L37">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M37">
-        <v>0.4545454545454545</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="N37">
-        <v>0.3636363636363636</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="38" spans="1:14">
@@ -5443,37 +5220,37 @@
         <v>208</v>
       </c>
       <c r="D38" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E38" t="s">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="F38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="I38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L38">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M38">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N38">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:14">
@@ -5487,10 +5264,10 @@
         <v>209</v>
       </c>
       <c r="D39" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E39" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -5499,7 +5276,7 @@
         <v>1</v>
       </c>
       <c r="H39" t="s">
-        <v>548</v>
+        <v>541</v>
       </c>
       <c r="I39" t="b">
         <v>1</v>
@@ -5531,37 +5308,37 @@
         <v>210</v>
       </c>
       <c r="D40" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="E40" t="s">
-        <v>484</v>
+        <v>463</v>
       </c>
       <c r="F40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
-        <v>549</v>
+        <v>542</v>
       </c>
       <c r="I40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K40">
         <v>4</v>
       </c>
       <c r="L40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M40">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N40">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -5575,10 +5352,10 @@
         <v>211</v>
       </c>
       <c r="D41" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E41" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -5587,7 +5364,7 @@
         <v>0</v>
       </c>
       <c r="H41" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -5619,10 +5396,10 @@
         <v>212</v>
       </c>
       <c r="D42" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E42" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -5631,7 +5408,7 @@
         <v>1</v>
       </c>
       <c r="H42" t="s">
-        <v>551</v>
+        <v>544</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
@@ -5663,10 +5440,10 @@
         <v>213</v>
       </c>
       <c r="D43" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="E43" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -5675,7 +5452,7 @@
         <v>1</v>
       </c>
       <c r="H43" t="s">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -5707,10 +5484,10 @@
         <v>214</v>
       </c>
       <c r="D44" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E44" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -5719,7 +5496,7 @@
         <v>1</v>
       </c>
       <c r="H44" t="s">
-        <v>553</v>
+        <v>546</v>
       </c>
       <c r="I44" t="b">
         <v>1</v>
@@ -5751,10 +5528,10 @@
         <v>215</v>
       </c>
       <c r="D45" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E45" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
@@ -5763,7 +5540,7 @@
         <v>1</v>
       </c>
       <c r="H45" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
@@ -5795,10 +5572,10 @@
         <v>216</v>
       </c>
       <c r="D46" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E46" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -5807,7 +5584,7 @@
         <v>1</v>
       </c>
       <c r="H46" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
       <c r="I46" t="b">
         <v>1</v>
@@ -5839,10 +5616,10 @@
         <v>217</v>
       </c>
       <c r="D47" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E47" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -5851,7 +5628,7 @@
         <v>1</v>
       </c>
       <c r="H47" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="I47" t="b">
         <v>1</v>
@@ -5883,10 +5660,10 @@
         <v>218</v>
       </c>
       <c r="D48" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E48" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -5895,7 +5672,7 @@
         <v>1</v>
       </c>
       <c r="H48" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="I48" t="b">
         <v>1</v>
@@ -5927,10 +5704,10 @@
         <v>219</v>
       </c>
       <c r="D49" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E49" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -5939,7 +5716,7 @@
         <v>1</v>
       </c>
       <c r="H49" t="s">
-        <v>558</v>
+        <v>551</v>
       </c>
       <c r="I49" t="b">
         <v>1</v>
@@ -5971,10 +5748,10 @@
         <v>220</v>
       </c>
       <c r="D50" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E50" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F50" t="b">
         <v>0</v>
@@ -5983,7 +5760,7 @@
         <v>0</v>
       </c>
       <c r="H50" t="s">
-        <v>559</v>
+        <v>552</v>
       </c>
       <c r="I50" t="b">
         <v>0</v>
@@ -6015,10 +5792,10 @@
         <v>221</v>
       </c>
       <c r="D51" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E51" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -6027,7 +5804,7 @@
         <v>1</v>
       </c>
       <c r="H51" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="I51" t="b">
         <v>1</v>
@@ -6059,10 +5836,10 @@
         <v>222</v>
       </c>
       <c r="D52" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="E52" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -6071,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="H52" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
       <c r="I52" t="b">
         <v>1</v>
@@ -6103,10 +5880,10 @@
         <v>223</v>
       </c>
       <c r="D53" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E53" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -6115,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="H53" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="I53" t="b">
         <v>1</v>
@@ -6147,10 +5924,10 @@
         <v>173</v>
       </c>
       <c r="D54" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E54" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -6159,7 +5936,7 @@
         <v>1</v>
       </c>
       <c r="H54" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="I54" t="b">
         <v>1</v>
@@ -6191,10 +5968,10 @@
         <v>224</v>
       </c>
       <c r="D55" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="E55" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -6203,7 +5980,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="I55" t="b">
         <v>1</v>
@@ -6235,10 +6012,10 @@
         <v>225</v>
       </c>
       <c r="D56" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E56" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F56" t="b">
         <v>0</v>
@@ -6247,7 +6024,7 @@
         <v>0</v>
       </c>
       <c r="H56" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="I56" t="b">
         <v>0</v>
@@ -6259,13 +6036,13 @@
         <v>6</v>
       </c>
       <c r="L56">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M56">
-        <v>0.5454545454545454</v>
+        <v>0.6</v>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="57" spans="1:14">
@@ -6279,34 +6056,34 @@
         <v>226</v>
       </c>
       <c r="D57" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E57" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G57" t="b">
         <v>0</v>
       </c>
       <c r="H57" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="I57" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J57" t="b">
         <v>0</v>
       </c>
       <c r="K57">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L57">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M57">
-        <v>0</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="N57">
         <v>0</v>
@@ -6323,37 +6100,37 @@
         <v>227</v>
       </c>
       <c r="D58" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="E58" t="s">
-        <v>490</v>
+        <v>465</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
       </c>
       <c r="G58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H58" t="s">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="I58" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J58" t="b">
         <v>0</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L58">
         <v>5</v>
       </c>
       <c r="M58">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N58">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:14">
@@ -6367,19 +6144,19 @@
         <v>228</v>
       </c>
       <c r="D59" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E59" t="s">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
       </c>
       <c r="G59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="s">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="I59" t="b">
         <v>1</v>
@@ -6388,16 +6165,16 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L59">
         <v>7</v>
       </c>
       <c r="M59">
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="N59">
-        <v>0.2857142857142857</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:14">
@@ -6411,19 +6188,19 @@
         <v>229</v>
       </c>
       <c r="D60" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E60" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F60" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G60" t="b">
         <v>0</v>
       </c>
       <c r="H60" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="I60" t="b">
         <v>0</v>
@@ -6432,16 +6209,16 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L60">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="M60">
-        <v>0.25</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="N60">
-        <v>0.1666666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:14">
@@ -6455,37 +6232,37 @@
         <v>230</v>
       </c>
       <c r="D61" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E61" t="s">
-        <v>493</v>
+        <v>465</v>
       </c>
       <c r="F61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="I61" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J61" t="b">
         <v>0</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L61">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="M61">
-        <v>0.07692307692307693</v>
+        <v>1</v>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:14">
@@ -6499,10 +6276,10 @@
         <v>231</v>
       </c>
       <c r="D62" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E62" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -6511,7 +6288,7 @@
         <v>1</v>
       </c>
       <c r="H62" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
       <c r="I62" t="b">
         <v>1</v>
@@ -6543,19 +6320,19 @@
         <v>232</v>
       </c>
       <c r="D63" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E63" t="s">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
       </c>
       <c r="G63" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="I63" t="b">
         <v>1</v>
@@ -6564,16 +6341,16 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L63">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M63">
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:14">
@@ -6587,37 +6364,37 @@
         <v>233</v>
       </c>
       <c r="D64" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="E64" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="F64" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G64" t="b">
         <v>0</v>
       </c>
       <c r="H64" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="I64" t="b">
         <v>0</v>
       </c>
       <c r="J64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64">
+        <v>3</v>
+      </c>
+      <c r="L64">
         <v>4</v>
       </c>
-      <c r="L64">
-        <v>5</v>
-      </c>
       <c r="M64">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="N64">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="65" spans="1:14">
@@ -6631,10 +6408,10 @@
         <v>234</v>
       </c>
       <c r="D65" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E65" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -6643,7 +6420,7 @@
         <v>1</v>
       </c>
       <c r="H65" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="I65" t="b">
         <v>1</v>
@@ -6675,10 +6452,10 @@
         <v>235</v>
       </c>
       <c r="D66" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E66" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
@@ -6687,7 +6464,7 @@
         <v>1</v>
       </c>
       <c r="H66" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="I66" t="b">
         <v>1</v>
@@ -6719,37 +6496,37 @@
         <v>236</v>
       </c>
       <c r="D67" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="E67" t="s">
-        <v>486</v>
+        <v>464</v>
       </c>
       <c r="F67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="I67" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J67" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L67">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M67">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N67">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:14">
@@ -6763,10 +6540,10 @@
         <v>237</v>
       </c>
       <c r="D68" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E68" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
@@ -6775,7 +6552,7 @@
         <v>0</v>
       </c>
       <c r="H68" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="I68" t="b">
         <v>1</v>
@@ -6807,37 +6584,37 @@
         <v>238</v>
       </c>
       <c r="D69" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E69" t="s">
-        <v>496</v>
+        <v>472</v>
       </c>
       <c r="F69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" t="s">
-        <v>562</v>
+        <v>555</v>
       </c>
       <c r="I69" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K69">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M69">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N69">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:14">
@@ -6851,10 +6628,10 @@
         <v>239</v>
       </c>
       <c r="D70" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E70" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
@@ -6863,7 +6640,7 @@
         <v>1</v>
       </c>
       <c r="H70" t="s">
-        <v>569</v>
+        <v>562</v>
       </c>
       <c r="I70" t="b">
         <v>1</v>
@@ -6895,22 +6672,22 @@
         <v>240</v>
       </c>
       <c r="D71" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E71" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
       </c>
       <c r="G71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="s">
-        <v>576</v>
+        <v>569</v>
       </c>
       <c r="I71" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J71" t="b">
         <v>0</v>
@@ -6919,13 +6696,13 @@
         <v>3</v>
       </c>
       <c r="L71">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M71">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N71">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:14">
@@ -6939,10 +6716,10 @@
         <v>241</v>
       </c>
       <c r="D72" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E72" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -6951,7 +6728,7 @@
         <v>1</v>
       </c>
       <c r="H72" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="I72" t="b">
         <v>1</v>
@@ -6983,10 +6760,10 @@
         <v>242</v>
       </c>
       <c r="D73" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E73" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
@@ -6995,7 +6772,7 @@
         <v>1</v>
       </c>
       <c r="H73" t="s">
-        <v>578</v>
+        <v>571</v>
       </c>
       <c r="I73" t="b">
         <v>1</v>
@@ -7027,10 +6804,10 @@
         <v>243</v>
       </c>
       <c r="D74" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E74" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -7039,7 +6816,7 @@
         <v>1</v>
       </c>
       <c r="H74" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="I74" t="b">
         <v>1</v>
@@ -7070,32 +6847,38 @@
       <c r="C75" t="s">
         <v>244</v>
       </c>
+      <c r="D75" t="s">
+        <v>391</v>
+      </c>
+      <c r="E75" t="s">
+        <v>472</v>
+      </c>
       <c r="F75" t="b">
         <v>1</v>
       </c>
       <c r="G75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H75" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="I75" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" t="b">
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L75">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76" spans="1:14">
@@ -7109,10 +6892,10 @@
         <v>245</v>
       </c>
       <c r="D76" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E76" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -7121,7 +6904,7 @@
         <v>1</v>
       </c>
       <c r="H76" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="I76" t="b">
         <v>1</v>
@@ -7153,10 +6936,10 @@
         <v>246</v>
       </c>
       <c r="D77" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E77" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -7165,7 +6948,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="s">
-        <v>582</v>
+        <v>575</v>
       </c>
       <c r="I77" t="b">
         <v>1</v>
@@ -7197,10 +6980,10 @@
         <v>247</v>
       </c>
       <c r="D78" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E78" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="F78" t="b">
         <v>0</v>
@@ -7209,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="H78" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="I78" t="b">
         <v>0</v>
@@ -7241,10 +7024,10 @@
         <v>248</v>
       </c>
       <c r="D79" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E79" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
@@ -7253,7 +7036,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="I79" t="b">
         <v>1</v>
@@ -7285,37 +7068,37 @@
         <v>249</v>
       </c>
       <c r="D80" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E80" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="I80" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J80" t="b">
         <v>0</v>
       </c>
       <c r="K80">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L80">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81" spans="1:14">
@@ -7329,10 +7112,10 @@
         <v>250</v>
       </c>
       <c r="D81" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="E81" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -7341,7 +7124,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="I81" t="b">
         <v>1</v>
@@ -7373,10 +7156,10 @@
         <v>251</v>
       </c>
       <c r="D82" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E82" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
@@ -7385,7 +7168,7 @@
         <v>1</v>
       </c>
       <c r="H82" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="I82" t="b">
         <v>1</v>
@@ -7417,10 +7200,10 @@
         <v>252</v>
       </c>
       <c r="D83" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="E83" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="F83" t="b">
         <v>0</v>
@@ -7429,7 +7212,7 @@
         <v>0</v>
       </c>
       <c r="H83" t="s">
-        <v>588</v>
+        <v>581</v>
       </c>
       <c r="I83" t="b">
         <v>0</v>
@@ -7441,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="L83">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M83">
         <v>0</v>
@@ -7461,10 +7244,10 @@
         <v>253</v>
       </c>
       <c r="D84" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E84" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F84" t="b">
         <v>0</v>
@@ -7473,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="I84" t="b">
         <v>0</v>
@@ -7505,10 +7288,10 @@
         <v>254</v>
       </c>
       <c r="D85" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E85" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -7517,7 +7300,7 @@
         <v>1</v>
       </c>
       <c r="H85" t="s">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="I85" t="b">
         <v>1</v>
@@ -7549,10 +7332,10 @@
         <v>255</v>
       </c>
       <c r="D86" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="E86" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
@@ -7561,7 +7344,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
       <c r="I86" t="b">
         <v>1</v>
@@ -7593,10 +7376,10 @@
         <v>256</v>
       </c>
       <c r="D87" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E87" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -7605,7 +7388,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="I87" t="b">
         <v>1</v>
@@ -7637,10 +7420,10 @@
         <v>257</v>
       </c>
       <c r="D88" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E88" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F88" t="b">
         <v>1</v>
@@ -7649,7 +7432,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="I88" t="b">
         <v>1</v>
@@ -7681,10 +7464,10 @@
         <v>258</v>
       </c>
       <c r="D89" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E89" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="F89" t="b">
         <v>0</v>
@@ -7693,7 +7476,7 @@
         <v>0</v>
       </c>
       <c r="H89" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="I89" t="b">
         <v>0</v>
@@ -7702,16 +7485,16 @@
         <v>0</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L89">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M89">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="N89">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="90" spans="1:14">
@@ -7725,10 +7508,10 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="E90" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F90" t="b">
         <v>1</v>
@@ -7737,7 +7520,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="I90" t="b">
         <v>1</v>
@@ -7769,10 +7552,10 @@
         <v>260</v>
       </c>
       <c r="D91" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E91" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F91" t="b">
         <v>1</v>
@@ -7781,7 +7564,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="I91" t="b">
         <v>1</v>
@@ -7813,10 +7596,10 @@
         <v>261</v>
       </c>
       <c r="D92" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E92" t="s">
-        <v>498</v>
+        <v>485</v>
       </c>
       <c r="F92" t="b">
         <v>0</v>
@@ -7825,25 +7608,25 @@
         <v>0</v>
       </c>
       <c r="H92" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="I92" t="b">
         <v>0</v>
       </c>
       <c r="J92" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L92">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M92">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="N92">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="93" spans="1:14">
@@ -7857,10 +7640,10 @@
         <v>262</v>
       </c>
       <c r="D93" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E93" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
@@ -7869,7 +7652,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="I93" t="b">
         <v>1</v>
@@ -7901,10 +7684,10 @@
         <v>263</v>
       </c>
       <c r="D94" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E94" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F94" t="b">
         <v>1</v>
@@ -7913,7 +7696,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="I94" t="b">
         <v>1</v>
@@ -7945,37 +7728,37 @@
         <v>264</v>
       </c>
       <c r="D95" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="E95" t="s">
-        <v>489</v>
+        <v>463</v>
       </c>
       <c r="F95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="s">
-        <v>599</v>
+        <v>592</v>
       </c>
       <c r="I95" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J95" t="b">
         <v>0</v>
       </c>
       <c r="K95">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L95">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:14">
@@ -7989,19 +7772,19 @@
         <v>265</v>
       </c>
       <c r="D96" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E96" t="s">
-        <v>499</v>
+        <v>463</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
       </c>
       <c r="G96" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H96" t="s">
-        <v>600</v>
+        <v>593</v>
       </c>
       <c r="I96" t="b">
         <v>1</v>
@@ -8010,16 +7793,16 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L96">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="M96">
-        <v>0.6666666666666666</v>
+        <v>1</v>
       </c>
       <c r="N96">
-        <v>0.3333333333333333</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:14">
@@ -8033,10 +7816,10 @@
         <v>266</v>
       </c>
       <c r="D97" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E97" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F97" t="b">
         <v>1</v>
@@ -8045,7 +7828,7 @@
         <v>1</v>
       </c>
       <c r="H97" t="s">
-        <v>601</v>
+        <v>594</v>
       </c>
       <c r="I97" t="b">
         <v>1</v>
@@ -8077,37 +7860,37 @@
         <v>267</v>
       </c>
       <c r="D98" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E98" t="s">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="F98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G98" t="b">
         <v>0</v>
       </c>
       <c r="H98" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="I98" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J98" t="b">
         <v>0</v>
       </c>
       <c r="K98">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M98">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="N98">
-        <v>1</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="99" spans="1:14">
@@ -8121,10 +7904,10 @@
         <v>268</v>
       </c>
       <c r="D99" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E99" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F99" t="b">
         <v>1</v>
@@ -8133,7 +7916,7 @@
         <v>1</v>
       </c>
       <c r="H99" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="I99" t="b">
         <v>1</v>
@@ -8165,10 +7948,10 @@
         <v>269</v>
       </c>
       <c r="D100" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E100" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
@@ -8177,7 +7960,7 @@
         <v>1</v>
       </c>
       <c r="H100" t="s">
-        <v>604</v>
+        <v>597</v>
       </c>
       <c r="I100" t="b">
         <v>1</v>
@@ -8209,37 +7992,37 @@
         <v>270</v>
       </c>
       <c r="D101" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="E101" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H101" t="s">
-        <v>605</v>
+        <v>598</v>
       </c>
       <c r="I101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J101" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L101">
         <v>2</v>
       </c>
       <c r="M101">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N101">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:14">
@@ -8253,10 +8036,10 @@
         <v>271</v>
       </c>
       <c r="D102" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="E102" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F102" t="b">
         <v>1</v>
@@ -8265,7 +8048,7 @@
         <v>1</v>
       </c>
       <c r="H102" t="s">
-        <v>606</v>
+        <v>599</v>
       </c>
       <c r="I102" t="b">
         <v>1</v>
@@ -8297,37 +8080,37 @@
         <v>272</v>
       </c>
       <c r="D103" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E103" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="F103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G103" t="b">
         <v>0</v>
       </c>
       <c r="H103" t="s">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="I103" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J103" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K103">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L103">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M103">
-        <v>0.8333333333333334</v>
+        <v>0.75</v>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="104" spans="1:14">
@@ -8341,10 +8124,10 @@
         <v>273</v>
       </c>
       <c r="D104" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="E104" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F104" t="b">
         <v>1</v>
@@ -8353,7 +8136,7 @@
         <v>1</v>
       </c>
       <c r="H104" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
       <c r="I104" t="b">
         <v>1</v>
@@ -8385,34 +8168,34 @@
         <v>274</v>
       </c>
       <c r="D105" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E105" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
       <c r="F105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105" t="b">
         <v>0</v>
       </c>
       <c r="H105" t="s">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="I105" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105" t="b">
         <v>0</v>
       </c>
       <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
         <v>3</v>
       </c>
-      <c r="L105">
-        <v>6</v>
-      </c>
       <c r="M105">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N105">
         <v>0</v>
@@ -8429,10 +8212,10 @@
         <v>275</v>
       </c>
       <c r="D106" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="E106" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F106" t="b">
         <v>1</v>
@@ -8441,7 +8224,7 @@
         <v>1</v>
       </c>
       <c r="H106" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="I106" t="b">
         <v>1</v>
@@ -8473,10 +8256,10 @@
         <v>276</v>
       </c>
       <c r="D107" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E107" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F107" t="b">
         <v>1</v>
@@ -8485,7 +8268,7 @@
         <v>1</v>
       </c>
       <c r="H107" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="I107" t="b">
         <v>1</v>
@@ -8517,10 +8300,10 @@
         <v>277</v>
       </c>
       <c r="D108" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E108" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F108" t="b">
         <v>1</v>
@@ -8529,7 +8312,7 @@
         <v>1</v>
       </c>
       <c r="H108" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="I108" t="b">
         <v>1</v>
@@ -8561,10 +8344,10 @@
         <v>278</v>
       </c>
       <c r="D109" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="E109" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="F109" t="b">
         <v>0</v>
@@ -8573,7 +8356,7 @@
         <v>0</v>
       </c>
       <c r="H109" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="I109" t="b">
         <v>0</v>
@@ -8585,13 +8368,13 @@
         <v>1</v>
       </c>
       <c r="L109">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M109">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
       <c r="N109">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="110" spans="1:14">
@@ -8605,10 +8388,10 @@
         <v>279</v>
       </c>
       <c r="D110" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E110" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F110" t="b">
         <v>1</v>
@@ -8617,7 +8400,7 @@
         <v>1</v>
       </c>
       <c r="H110" t="s">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="I110" t="b">
         <v>1</v>
@@ -8649,10 +8432,10 @@
         <v>280</v>
       </c>
       <c r="D111" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E111" t="s">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="F111" t="b">
         <v>0</v>
@@ -8661,22 +8444,22 @@
         <v>0</v>
       </c>
       <c r="H111" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="I111" t="b">
         <v>0</v>
       </c>
       <c r="J111" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L111">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="M111">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="N111">
         <v>0</v>
@@ -8693,10 +8476,10 @@
         <v>281</v>
       </c>
       <c r="D112" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="E112" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F112" t="b">
         <v>1</v>
@@ -8705,7 +8488,7 @@
         <v>1</v>
       </c>
       <c r="H112" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="I112" t="b">
         <v>1</v>
@@ -8737,10 +8520,10 @@
         <v>236</v>
       </c>
       <c r="D113" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E113" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F113" t="b">
         <v>0</v>
@@ -8749,7 +8532,7 @@
         <v>0</v>
       </c>
       <c r="H113" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="I113" t="b">
         <v>0</v>
@@ -8781,10 +8564,10 @@
         <v>238</v>
       </c>
       <c r="D114" t="s">
-        <v>351</v>
+        <v>429</v>
       </c>
       <c r="E114" t="s">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="F114" t="b">
         <v>0</v>
@@ -8793,7 +8576,7 @@
         <v>0</v>
       </c>
       <c r="H114" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="I114" t="b">
         <v>0</v>
@@ -8825,22 +8608,22 @@
         <v>240</v>
       </c>
       <c r="D115" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="E115" t="s">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="F115" t="b">
         <v>1</v>
       </c>
       <c r="G115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="I115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J115" t="b">
         <v>0</v>
@@ -8849,13 +8632,13 @@
         <v>3</v>
       </c>
       <c r="L115">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M115">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="N115">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116" spans="1:14">
@@ -8869,10 +8652,10 @@
         <v>282</v>
       </c>
       <c r="D116" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="E116" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="F116" t="b">
         <v>0</v>
@@ -8881,25 +8664,25 @@
         <v>0</v>
       </c>
       <c r="H116" t="s">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="I116" t="b">
         <v>0</v>
       </c>
       <c r="J116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K116">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L116">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="M116">
-        <v>0.6363636363636364</v>
+        <v>0</v>
       </c>
       <c r="N116">
-        <v>0.1818181818181818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:14">
@@ -8913,10 +8696,10 @@
         <v>283</v>
       </c>
       <c r="D117" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="E117" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F117" t="b">
         <v>1</v>
@@ -8925,7 +8708,7 @@
         <v>1</v>
       </c>
       <c r="H117" t="s">
-        <v>620</v>
+        <v>613</v>
       </c>
       <c r="I117" t="b">
         <v>1</v>
@@ -8957,10 +8740,10 @@
         <v>284</v>
       </c>
       <c r="D118" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="E118" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F118" t="b">
         <v>1</v>
@@ -8969,7 +8752,7 @@
         <v>1</v>
       </c>
       <c r="H118" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="I118" t="b">
         <v>1</v>
@@ -9001,10 +8784,10 @@
         <v>285</v>
       </c>
       <c r="D119" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="E119" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="F119" t="b">
         <v>1</v>
@@ -9013,7 +8796,7 @@
         <v>1</v>
       </c>
       <c r="H119" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="I119" t="b">
         <v>1</v>
@@ -9045,10 +8828,10 @@
         <v>286</v>
       </c>
       <c r="D120" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="E120" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F120" t="b">
         <v>1</v>
@@ -9057,7 +8840,7 @@
         <v>1</v>
       </c>
       <c r="H120" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="I120" t="b">
         <v>1</v>
@@ -9089,10 +8872,10 @@
         <v>287</v>
       </c>
       <c r="D121" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="E121" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F121" t="b">
         <v>1</v>
@@ -9101,7 +8884,7 @@
         <v>1</v>
       </c>
       <c r="H121" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="I121" t="b">
         <v>1</v>
@@ -9136,7 +8919,7 @@
         <v>319</v>
       </c>
       <c r="E122" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="F122" t="b">
         <v>1</v>
@@ -9145,7 +8928,7 @@
         <v>1</v>
       </c>
       <c r="H122" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="I122" t="b">
         <v>1</v>
@@ -9177,10 +8960,10 @@
         <v>289</v>
       </c>
       <c r="D123" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E123" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F123" t="b">
         <v>1</v>
@@ -9189,7 +8972,7 @@
         <v>1</v>
       </c>
       <c r="H123" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="I123" t="b">
         <v>1</v>
@@ -9221,37 +9004,37 @@
         <v>290</v>
       </c>
       <c r="D124" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E124" t="s">
-        <v>504</v>
+        <v>463</v>
       </c>
       <c r="F124" t="b">
         <v>1</v>
       </c>
       <c r="G124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="I124" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J124" t="b">
         <v>0</v>
       </c>
       <c r="K124">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L124">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M124">
-        <v>0.2727272727272727</v>
+        <v>1</v>
       </c>
       <c r="N124">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:14">
@@ -9265,22 +9048,22 @@
         <v>291</v>
       </c>
       <c r="D125" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E125" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="F125" t="b">
         <v>1</v>
       </c>
       <c r="G125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="I125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J125" t="b">
         <v>0</v>
@@ -9289,13 +9072,13 @@
         <v>3</v>
       </c>
       <c r="L125">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M125">
-        <v>0.2727272727272727</v>
+        <v>1</v>
       </c>
       <c r="N125">
-        <v>0.1818181818181818</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:14">
@@ -9309,10 +9092,10 @@
         <v>292</v>
       </c>
       <c r="D126" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="E126" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F126" t="b">
         <v>1</v>
@@ -9321,7 +9104,7 @@
         <v>1</v>
       </c>
       <c r="H126" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="I126" t="b">
         <v>1</v>
@@ -9353,37 +9136,37 @@
         <v>293</v>
       </c>
       <c r="D127" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="E127" t="s">
-        <v>486</v>
+        <v>463</v>
       </c>
       <c r="F127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H127" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="I127" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K127">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L127">
         <v>4</v>
       </c>
       <c r="M127">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="N127">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:14">
@@ -9397,10 +9180,10 @@
         <v>294</v>
       </c>
       <c r="D128" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="E128" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="F128" t="b">
         <v>0</v>
@@ -9409,7 +9192,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="I128" t="b">
         <v>0</v>
@@ -9418,16 +9201,16 @@
         <v>1</v>
       </c>
       <c r="K128">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L128">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M128">
-        <v>0.25</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N128">
-        <v>0.125</v>
+        <v>0.3333333333333333</v>
       </c>
     </row>
     <row r="129" spans="1:14">
@@ -9441,10 +9224,10 @@
         <v>295</v>
       </c>
       <c r="D129" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E129" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="F129" t="b">
         <v>0</v>
@@ -9453,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="H129" t="s">
-        <v>631</v>
+        <v>624</v>
       </c>
       <c r="I129" t="b">
         <v>0</v>
@@ -9485,10 +9268,10 @@
         <v>296</v>
       </c>
       <c r="D130" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="E130" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F130" t="b">
         <v>1</v>
@@ -9497,7 +9280,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="s">
-        <v>632</v>
+        <v>625</v>
       </c>
       <c r="I130" t="b">
         <v>1</v>
@@ -9529,10 +9312,10 @@
         <v>297</v>
       </c>
       <c r="D131" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="E131" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F131" t="b">
         <v>1</v>
@@ -9541,7 +9324,7 @@
         <v>1</v>
       </c>
       <c r="H131" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="I131" t="b">
         <v>1</v>
@@ -9573,37 +9356,37 @@
         <v>298</v>
       </c>
       <c r="D132" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E132" t="s">
-        <v>460</v>
+        <v>499</v>
       </c>
       <c r="F132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G132" t="b">
         <v>0</v>
       </c>
       <c r="H132" t="s">
-        <v>634</v>
+        <v>627</v>
       </c>
       <c r="I132" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J132" t="b">
         <v>0</v>
       </c>
       <c r="K132">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L132">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M132">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="N132">
-        <v>1</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="133" spans="1:14">
@@ -9617,10 +9400,10 @@
         <v>299</v>
       </c>
       <c r="D133" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="E133" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F133" t="b">
         <v>1</v>
@@ -9629,7 +9412,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="s">
-        <v>635</v>
+        <v>628</v>
       </c>
       <c r="I133" t="b">
         <v>1</v>
@@ -9661,10 +9444,10 @@
         <v>300</v>
       </c>
       <c r="D134" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E134" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F134" t="b">
         <v>1</v>
@@ -9673,7 +9456,7 @@
         <v>1</v>
       </c>
       <c r="H134" t="s">
-        <v>636</v>
+        <v>629</v>
       </c>
       <c r="I134" t="b">
         <v>1</v>
@@ -9705,10 +9488,10 @@
         <v>301</v>
       </c>
       <c r="D135" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="E135" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="F135" t="b">
         <v>1</v>
@@ -9717,7 +9500,7 @@
         <v>1</v>
       </c>
       <c r="H135" t="s">
-        <v>637</v>
+        <v>630</v>
       </c>
       <c r="I135" t="b">
         <v>1</v>
@@ -9749,19 +9532,19 @@
         <v>302</v>
       </c>
       <c r="D136" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="E136" t="s">
-        <v>507</v>
+        <v>500</v>
       </c>
       <c r="F136" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136" t="b">
         <v>0</v>
       </c>
       <c r="H136" t="s">
-        <v>638</v>
+        <v>631</v>
       </c>
       <c r="I136" t="b">
         <v>0</v>
@@ -9770,16 +9553,16 @@
         <v>0</v>
       </c>
       <c r="K136">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L136">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M136">
-        <v>0.3636363636363636</v>
+        <v>0.2</v>
       </c>
       <c r="N136">
-        <v>0.1818181818181818</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="137" spans="1:14">
@@ -9793,10 +9576,10 @@
         <v>303</v>
       </c>
       <c r="D137" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="E137" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
       <c r="F137" t="b">
         <v>0</v>
@@ -9805,7 +9588,7 @@
         <v>0</v>
       </c>
       <c r="H137" t="s">
-        <v>639</v>
+        <v>632</v>
       </c>
       <c r="I137" t="b">
         <v>0</v>
@@ -9814,16 +9597,16 @@
         <v>0</v>
       </c>
       <c r="K137">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L137">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M137">
-        <v>0.4</v>
+        <v>0.4545454545454545</v>
       </c>
       <c r="N137">
-        <v>0.4</v>
+        <v>0.3636363636363636</v>
       </c>
     </row>
     <row r="138" spans="1:14">
@@ -9837,10 +9620,10 @@
         <v>304</v>
       </c>
       <c r="D138" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="E138" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F138" t="b">
         <v>1</v>
@@ -9849,7 +9632,7 @@
         <v>1</v>
       </c>
       <c r="H138" t="s">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="I138" t="b">
         <v>1</v>
@@ -9881,19 +9664,19 @@
         <v>305</v>
       </c>
       <c r="D139" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E139" t="s">
-        <v>509</v>
+        <v>472</v>
       </c>
       <c r="F139" t="b">
         <v>1</v>
       </c>
       <c r="G139" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H139" t="s">
-        <v>641</v>
+        <v>634</v>
       </c>
       <c r="I139" t="b">
         <v>1</v>
@@ -9902,16 +9685,16 @@
         <v>0</v>
       </c>
       <c r="K139">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L139">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M139">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140" spans="1:14">
@@ -9925,37 +9708,37 @@
         <v>306</v>
       </c>
       <c r="D140" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="E140" t="s">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="F140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="s">
-        <v>642</v>
+        <v>635</v>
       </c>
       <c r="I140" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J140" t="b">
         <v>0</v>
       </c>
       <c r="K140">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L140">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:14">
@@ -9969,10 +9752,10 @@
         <v>307</v>
       </c>
       <c r="D141" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="E141" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="F141" t="b">
         <v>0</v>
@@ -9981,7 +9764,7 @@
         <v>0</v>
       </c>
       <c r="H141" t="s">
-        <v>512</v>
+        <v>505</v>
       </c>
       <c r="I141" t="b">
         <v>0</v>
@@ -9990,16 +9773,16 @@
         <v>1</v>
       </c>
       <c r="K141">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L141">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M141">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="N141">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="142" spans="1:14">
@@ -10013,10 +9796,10 @@
         <v>308</v>
       </c>
       <c r="D142" t="s">
-        <v>450</v>
+        <v>394</v>
       </c>
       <c r="E142" t="s">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="F142" t="b">
         <v>0</v>
@@ -10025,7 +9808,7 @@
         <v>0</v>
       </c>
       <c r="H142" t="s">
-        <v>643</v>
+        <v>636</v>
       </c>
       <c r="I142" t="b">
         <v>0</v>
@@ -10034,16 +9817,16 @@
         <v>1</v>
       </c>
       <c r="K142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L142">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M142">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N142">
-        <v>0.5</v>
+        <v>0.6666666666666666</v>
       </c>
     </row>
     <row r="143" spans="1:14">
@@ -10057,10 +9840,10 @@
         <v>309</v>
       </c>
       <c r="D143" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E143" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F143" t="b">
         <v>1</v>
@@ -10069,7 +9852,7 @@
         <v>1</v>
       </c>
       <c r="H143" t="s">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="I143" t="b">
         <v>1</v>
@@ -10101,10 +9884,10 @@
         <v>310</v>
       </c>
       <c r="D144" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E144" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="F144" t="b">
         <v>1</v>
@@ -10113,7 +9896,7 @@
         <v>1</v>
       </c>
       <c r="H144" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="I144" t="b">
         <v>1</v>
@@ -10145,10 +9928,10 @@
         <v>311</v>
       </c>
       <c r="D145" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E145" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F145" t="b">
         <v>1</v>
@@ -10157,7 +9940,7 @@
         <v>1</v>
       </c>
       <c r="H145" t="s">
-        <v>646</v>
+        <v>639</v>
       </c>
       <c r="I145" t="b">
         <v>1</v>
@@ -10189,10 +9972,10 @@
         <v>312</v>
       </c>
       <c r="D146" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E146" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F146" t="b">
         <v>1</v>
@@ -10201,7 +9984,7 @@
         <v>1</v>
       </c>
       <c r="H146" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
       <c r="I146" t="b">
         <v>1</v>
@@ -10233,10 +10016,10 @@
         <v>313</v>
       </c>
       <c r="D147" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="E147" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="F147" t="b">
         <v>0</v>
@@ -10245,7 +10028,7 @@
         <v>0</v>
       </c>
       <c r="H147" t="s">
-        <v>647</v>
+        <v>640</v>
       </c>
       <c r="I147" t="b">
         <v>0</v>
@@ -10254,16 +10037,16 @@
         <v>0</v>
       </c>
       <c r="K147">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L147">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M147">
-        <v>0.6666666666666666</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="N147">
-        <v>0.6666666666666666</v>
+        <v>0.2222222222222222</v>
       </c>
     </row>
     <row r="148" spans="1:14">
@@ -10277,10 +10060,10 @@
         <v>314</v>
       </c>
       <c r="D148" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E148" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F148" t="b">
         <v>1</v>
@@ -10289,7 +10072,7 @@
         <v>1</v>
       </c>
       <c r="H148" t="s">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="I148" t="b">
         <v>1</v>
@@ -10321,10 +10104,10 @@
         <v>315</v>
       </c>
       <c r="D149" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="E149" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="F149" t="b">
         <v>1</v>
@@ -10333,7 +10116,7 @@
         <v>1</v>
       </c>
       <c r="H149" t="s">
-        <v>649</v>
+        <v>642</v>
       </c>
       <c r="I149" t="b">
         <v>1</v>
@@ -10365,10 +10148,10 @@
         <v>316</v>
       </c>
       <c r="D150" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E150" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F150" t="b">
         <v>1</v>
@@ -10377,7 +10160,7 @@
         <v>1</v>
       </c>
       <c r="H150" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="I150" t="b">
         <v>1</v>
@@ -10409,10 +10192,10 @@
         <v>317</v>
       </c>
       <c r="D151" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="E151" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="F151" t="b">
         <v>1</v>
@@ -10421,7 +10204,7 @@
         <v>1</v>
       </c>
       <c r="H151" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="I151" t="b">
         <v>1</v>
